--- a/output_plant/stomataKonrad_Intermediate_combined.xlsx
+++ b/output_plant/stomataKonrad_Intermediate_combined.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
   <si>
     <t>eDab</t>
   </si>
@@ -498,6 +498,120 @@
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">Kleinsaubernitz; Guttau Volcano Group; SPP zone 20 G; neptuni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.palaeo.2012.12.025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stomata-konrad-fom_grein_2013.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harper and Giulivi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biostratigraphy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angiosperm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 sigma; source 2 sigma divided by 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">from compilation presented in Table S1 of Kowalczyk et al. (2018) for evergreen angiosperms in an evergreen warm mixed forest biome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generic value from Franks et al. (2014); 1 sigma error is 5% of mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pore length measured directly, so this scalar has no error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pore depth measured directly, so this scalar has no error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generic value for angiosperms from Franks et al. (2014); 1 sigma error is 5% of mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pore length stored in GCLab (s1=1); pore depth stored in GCWab (s2=1). Density converted to m^-2; lengths to m; measured 2 sigma errors converted to 1 sigma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kleinsaubernitz; Guttau Volcano Group; SPP zone 20 G; furcinervis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kleinsaubernitz; Guttau Volcano Group; SPP zone 20 G; praerhenana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borna-Ost-Bockwitz TC; Cottbus Formation; Thierbach member. SPP zone 17/18; neptuni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biostratigraphy. Base of Thierbach is dated to 25.3 Ma and this site is from the third sedimentation cycle from the bottom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borna-Ost-Bockwitz TC; Cottbus Formation; Thierbach member. SPP zone 17/18; acutimontanum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witznitz WC; Cottbus Formation; Thierbach member. SPP zone 17/18; neptuni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biostratigraphy. Latest Oligocene to Oligocene-Miocen boundary. See Roth-Nebelsick et al., 2012.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witznitz WC; Cottbus Formation; Thierbach member. SPP zone 17/18; furcinervis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witznitz WC; Cottbus Formation; Thierbach member. SPP zone 17/18; pseudoprinceps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Witznitz WC; Cottbus Formation; Thierbach member. SPP zone 17/18; acutimontanum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oberdorf; Koflach / Voitsberg lignite mining; rhenana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biostratigraphy and magetostratigraphy. Mammals fall within Chron c5Dn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiesa; SPN Zone VI A. Lausitz mining area; pseudoprinceps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biostratigraphy. Middle Burdigalian.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhynie Chert; major</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/S0031-0182(03)00634-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stomata-konrad-fom_roth-nebelsick_2003.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biostratigraphy (Pragian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglaophyton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: this publication does not use the standard Konrad 2008 gas-exchange model to estimate CO2. It uses a different leaf gas-exchange model that has not been used by any other subsequent papers; Pore length stored in GCLab (s1=1); pore depth stored in GCWab (s2=1). Density converted to m^-2; lengths to m; measured 2 sigma errors converted to 1 sigma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhynie Chert; gwynne-vaughanii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhynia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhynie Chert; aphylla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Budapest, H-boreholes (Hungary); Tard clay Formation; NP23; olmediaefolia</t>
   </si>
   <si>
@@ -513,31 +627,7 @@
     <t xml:space="preserve">droyer@wesleyan.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">biostratigraphy, nannoplankton, NP23 zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angiosperm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 sigma; source 2 sigma divided by 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">from compilation presented in Table S1 of Kowalczyk et al. (2018) for evergreen angiosperms in an evergreen warm mixed forest biome.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generic value from Franks et al. (2014); 1 sigma error is 5% of mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pore length measured directly, so this scalar has no error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pore depth measured directly, so this scalar has no error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generic value for angiosperms from Franks et al. (2014); 1 sigma error is 5% of mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">modified from the more elaborate Konrad model template to fit Franks model template; Pore length stored in GCLab (s1=1); pore depth stored in GCWab (s2=1). Density converted to m^-2; lengths to m; measured 2 sigma errors converted to 1 sigma.</t>
+    <t xml:space="preserve">biostratigraphy, nannoplankton, NP23 zone; Biostratigraphy updated to GTS2020</t>
   </si>
   <si>
     <t xml:space="preserve">Budapest, Nagybátony-Újlak (Hungary); Tard clay Formation; NP23; olmediaefolia</t>
@@ -652,6 +742,21 @@
   </si>
   <si>
     <t xml:space="preserve">Wz 194-196/88,Wz 214/88,Wz 226/88,Wz 239/88,Wz 248/88,Wz 255/88,Wz 266/88; Witznitz  Open cast mining; Cottbus Formation; Thierbach member; Platanus neptuni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guangxi, China; Oligocene; Ningming Formation; ningmingensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016/j.palaeo.2016.09.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stomata-konrad-rom_sun_2017_p1.0.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palynostratigraphy and lithostratigraphy (Oligocene); Biostratigraphy updated to GTS2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guangxi, China; Oligocene; Ningming Formation; slenderifolius</t>
   </si>
 </sst>
 </file>
@@ -1762,18 +1867,18 @@
         <v>165</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>47.5333333333333</v>
+        <v>51.27</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>19.0333333333333</v>
+        <v>14.59</v>
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
       <c r="J4" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="K4" s="22" t="n">
         <v>27</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>32</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>166</v>
@@ -1782,10 +1887,10 @@
         <v>167</v>
       </c>
       <c r="N4" s="24" t="n">
-        <v>646000000</v>
+        <v>105000000</v>
       </c>
       <c r="O4" s="24" t="n">
-        <v>39375000</v>
+        <v>25500000</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>168</v>
@@ -1798,14 +1903,10 @@
       </c>
       <c r="S4" s="1"/>
       <c r="T4" s="24" t="n">
-        <v>0.00000295</v>
-      </c>
-      <c r="U4" s="24" t="n">
-        <v>0.00000018</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>168</v>
-      </c>
+        <v>0.00001417</v>
+      </c>
+      <c r="U4" s="24"/>
+      <c r="V4" s="1"/>
       <c r="W4" s="24" t="n">
         <v>0</v>
       </c>
@@ -1814,10 +1915,14 @@
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="24" t="n">
-        <v>0.00001</v>
-      </c>
-      <c r="AA4" s="24"/>
-      <c r="AB4" s="1"/>
+        <v>0.0000144</v>
+      </c>
+      <c r="AA4" s="24" t="n">
+        <v>0.000000755</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="AC4" s="24" t="n">
         <v>0</v>
       </c>
@@ -1826,10 +1931,10 @@
       </c>
       <c r="AE4" s="1"/>
       <c r="AF4" s="20" t="n">
-        <v>-28.54</v>
+        <v>-27.09</v>
       </c>
       <c r="AG4" s="20" t="n">
-        <v>0.54</v>
+        <v>0.265</v>
       </c>
       <c r="AH4" s="1" t="s">
         <v>168</v>
@@ -1927,18 +2032,18 @@
         <v>165</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>47.5333333333333</v>
+        <v>51.27</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>19.0333333333333</v>
+        <v>14.59</v>
       </c>
       <c r="H5" s="22"/>
       <c r="I5" s="22"/>
       <c r="J5" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="K5" s="22" t="n">
         <v>27</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>32</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>166</v>
@@ -1947,10 +2052,10 @@
         <v>167</v>
       </c>
       <c r="N5" s="26" t="n">
-        <v>646000000</v>
+        <v>725000000</v>
       </c>
       <c r="O5" s="26" t="n">
-        <v>53000000</v>
+        <v>111500000</v>
       </c>
       <c r="P5" t="s">
         <v>168</v>
@@ -1963,10 +2068,10 @@
       </c>
       <c r="S5"/>
       <c r="T5" s="26" t="n">
-        <v>0.00000331</v>
+        <v>0.00000889</v>
       </c>
       <c r="U5" s="26" t="n">
-        <v>0.00000042</v>
+        <v>0.00000039</v>
       </c>
       <c r="V5" t="s">
         <v>168</v>
@@ -1979,10 +2084,14 @@
       </c>
       <c r="Y5"/>
       <c r="Z5" s="24" t="n">
-        <v>0.00001</v>
-      </c>
-      <c r="AA5" s="24"/>
-      <c r="AB5" s="1"/>
+        <v>0.0000113</v>
+      </c>
+      <c r="AA5" s="24" t="n">
+        <v>0.00000095</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="AC5" s="24" t="n">
         <v>0</v>
       </c>
@@ -1991,10 +2100,10 @@
       </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="25" t="n">
-        <v>-28.54</v>
+        <v>-29.68</v>
       </c>
       <c r="AG5" s="25" t="n">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="AH5" t="s">
         <v>168</v>
@@ -2092,18 +2201,18 @@
         <v>165</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>45.9833333333333</v>
+        <v>51.27</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>14.1666666666667</v>
+        <v>14.59</v>
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
       <c r="J6" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="K6" s="22" t="n">
         <v>27</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>32</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>166</v>
@@ -2112,10 +2221,10 @@
         <v>167</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>700000000</v>
+        <v>345000000</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>79000000</v>
+        <v>49500000</v>
       </c>
       <c r="P6" t="s">
         <v>168</v>
@@ -2128,10 +2237,10 @@
       </c>
       <c r="S6"/>
       <c r="T6" s="26" t="n">
-        <v>0.00000325</v>
+        <v>0.00000825</v>
       </c>
       <c r="U6" s="26" t="n">
-        <v>0.000000725</v>
+        <v>0.00000048</v>
       </c>
       <c r="V6" t="s">
         <v>168</v>
@@ -2144,10 +2253,14 @@
       </c>
       <c r="Y6"/>
       <c r="Z6" s="24" t="n">
-        <v>0.00001</v>
-      </c>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="1"/>
+        <v>0.00000886</v>
+      </c>
+      <c r="AA6" s="24" t="n">
+        <v>0.000000815</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>168</v>
+      </c>
       <c r="AC6" s="24" t="n">
         <v>0</v>
       </c>
@@ -2156,10 +2269,10 @@
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="25" t="n">
-        <v>-28.25</v>
+        <v>-29.68</v>
       </c>
       <c r="AG6" s="25" t="n">
-        <v>0.07</v>
+        <v>0.46</v>
       </c>
       <c r="AH6" t="s">
         <v>168</v>
@@ -2245,10 +2358,10 @@
         <v>177</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>164</v>
@@ -2257,30 +2370,30 @@
         <v>165</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>49.91</v>
+        <v>51.12</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I7" s="22" t="n">
-        <v>0.199999999999996</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
+        <v>12.54</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>25.5</v>
+      </c>
       <c r="L7" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>167</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>282000000</v>
+        <v>100000000</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>29500000</v>
+        <v>16500000</v>
       </c>
       <c r="P7" t="s">
         <v>168</v>
@@ -2293,14 +2406,10 @@
       </c>
       <c r="S7"/>
       <c r="T7" s="26" t="n">
-        <v>0.00000756</v>
-      </c>
-      <c r="U7" s="26" t="n">
-        <v>0.000001</v>
-      </c>
-      <c r="V7" t="s">
-        <v>168</v>
-      </c>
+        <v>0.00001483</v>
+      </c>
+      <c r="U7" s="26"/>
+      <c r="V7"/>
       <c r="W7" s="24" t="n">
         <v>0</v>
       </c>
@@ -2309,10 +2418,10 @@
       </c>
       <c r="Y7"/>
       <c r="Z7" s="24" t="n">
-        <v>0.0000132</v>
+        <v>0.0000137</v>
       </c>
       <c r="AA7" s="24" t="n">
-        <v>0.00000065</v>
+        <v>0.000000535</v>
       </c>
       <c r="AB7" s="1" t="s">
         <v>168</v>
@@ -2325,10 +2434,10 @@
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="25" t="n">
-        <v>-27.6</v>
+        <v>-26.95</v>
       </c>
       <c r="AG7" s="25" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="AH7" t="s">
         <v>168</v>
@@ -2411,13 +2520,13 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>164</v>
@@ -2426,27 +2535,27 @@
         <v>165</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>49.91</v>
+        <v>51.12</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>0.199999999999996</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
+        <v>12.54</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>25.5</v>
+      </c>
       <c r="L8" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>167</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>410000000</v>
+        <v>251000000</v>
       </c>
       <c r="O8" s="26" t="n">
         <v>32500000</v>
@@ -2462,10 +2571,10 @@
       </c>
       <c r="S8"/>
       <c r="T8" s="26" t="n">
-        <v>0.00000712</v>
+        <v>0.00000626</v>
       </c>
       <c r="U8" s="26" t="n">
-        <v>0.00000075</v>
+        <v>0.000000195</v>
       </c>
       <c r="V8" t="s">
         <v>168</v>
@@ -2494,10 +2603,10 @@
       </c>
       <c r="AE8" s="1"/>
       <c r="AF8" s="25" t="n">
-        <v>-28.7</v>
+        <v>-27.29</v>
       </c>
       <c r="AG8" s="25" t="n">
-        <v>0.4</v>
+        <v>0.54</v>
       </c>
       <c r="AH8" t="s">
         <v>168</v>
@@ -2580,13 +2689,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="D9" t="s">
         <v>164</v>
@@ -2595,30 +2704,30 @@
         <v>165</v>
       </c>
       <c r="F9" t="n">
-        <v>49.91</v>
+        <v>51.17</v>
       </c>
       <c r="G9" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>0.199999999999996</v>
-      </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
+        <v>12.5</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>24.5</v>
+      </c>
       <c r="L9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M9" t="s">
         <v>167</v>
       </c>
       <c r="N9" t="n">
-        <v>327000000</v>
+        <v>97000000</v>
       </c>
       <c r="O9" t="n">
-        <v>23000000</v>
+        <v>7050000</v>
       </c>
       <c r="P9" t="s">
         <v>168</v>
@@ -2631,14 +2740,10 @@
       </c>
       <c r="S9"/>
       <c r="T9" t="n">
-        <v>0.00000629</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.00000065</v>
-      </c>
-      <c r="V9" t="s">
-        <v>168</v>
-      </c>
+        <v>0.00001428</v>
+      </c>
+      <c r="U9"/>
+      <c r="V9"/>
       <c r="W9" t="n">
         <v>0</v>
       </c>
@@ -2647,10 +2752,10 @@
       </c>
       <c r="Y9"/>
       <c r="Z9" t="n">
-        <v>0.0000163</v>
+        <v>0.0000141</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0000005</v>
+        <v>0.00000028</v>
       </c>
       <c r="AB9" t="s">
         <v>168</v>
@@ -2663,10 +2768,10 @@
       </c>
       <c r="AE9"/>
       <c r="AF9" t="n">
-        <v>-29.5</v>
+        <v>-27.24</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.35</v>
+        <v>0.215</v>
       </c>
       <c r="AH9" t="s">
         <v>168</v>
@@ -2749,13 +2854,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D10" t="s">
         <v>164</v>
@@ -2763,27 +2868,31 @@
       <c r="E10" t="s">
         <v>165</v>
       </c>
-      <c r="F10"/>
-      <c r="G10"/>
+      <c r="F10" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.5</v>
+      </c>
       <c r="H10" s="22"/>
       <c r="I10" s="22"/>
       <c r="J10" s="22" t="n">
-        <v>35.4</v>
+        <v>23</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>35.8</v>
+        <v>24.5</v>
       </c>
       <c r="L10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M10" t="s">
         <v>167</v>
       </c>
       <c r="N10" t="n">
-        <v>259000000</v>
+        <v>614000000</v>
       </c>
       <c r="O10" t="n">
-        <v>55000000</v>
+        <v>46500000</v>
       </c>
       <c r="P10" t="s">
         <v>168</v>
@@ -2796,10 +2905,10 @@
       </c>
       <c r="S10"/>
       <c r="T10" t="n">
-        <v>0.0000075</v>
+        <v>0.00000893</v>
       </c>
       <c r="U10" t="n">
-        <v>0.00000085</v>
+        <v>0.00000041</v>
       </c>
       <c r="V10" t="s">
         <v>168</v>
@@ -2812,10 +2921,10 @@
       </c>
       <c r="Y10"/>
       <c r="Z10" t="n">
-        <v>0.00001165</v>
+        <v>0.0000113</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00000075</v>
+        <v>0.00000095</v>
       </c>
       <c r="AB10" t="s">
         <v>168</v>
@@ -2828,10 +2937,14 @@
       </c>
       <c r="AE10"/>
       <c r="AF10" t="n">
-        <v>-27.37</v>
-      </c>
-      <c r="AG10"/>
-      <c r="AH10"/>
+        <v>-27.62</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>168</v>
+      </c>
       <c r="AI10" t="n">
         <v>360</v>
       </c>
@@ -2910,13 +3023,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D11" t="s">
         <v>164</v>
@@ -2924,27 +3037,31 @@
       <c r="E11" t="s">
         <v>165</v>
       </c>
-      <c r="F11"/>
-      <c r="G11"/>
+      <c r="F11" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.5</v>
+      </c>
       <c r="H11" s="22"/>
       <c r="I11" s="22"/>
       <c r="J11" s="22" t="n">
-        <v>36.2</v>
+        <v>23</v>
       </c>
       <c r="K11" s="22" t="n">
-        <v>36.4</v>
+        <v>24.5</v>
       </c>
       <c r="L11" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M11" t="s">
         <v>167</v>
       </c>
       <c r="N11" t="n">
-        <v>299000000</v>
+        <v>297000000</v>
       </c>
       <c r="O11" t="n">
-        <v>48000000</v>
+        <v>10900000</v>
       </c>
       <c r="P11" t="s">
         <v>168</v>
@@ -2957,10 +3074,10 @@
       </c>
       <c r="S11"/>
       <c r="T11" t="n">
-        <v>0.00000683</v>
+        <v>0.00000673</v>
       </c>
       <c r="U11" t="n">
-        <v>0.00000064</v>
+        <v>0.00000033</v>
       </c>
       <c r="V11" t="s">
         <v>168</v>
@@ -2973,10 +3090,10 @@
       </c>
       <c r="Y11"/>
       <c r="Z11" t="n">
-        <v>0.00001103</v>
+        <v>0.0000218</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.000000665</v>
+        <v>0.0000007</v>
       </c>
       <c r="AB11" t="s">
         <v>168</v>
@@ -2989,10 +3106,14 @@
       </c>
       <c r="AE11"/>
       <c r="AF11" t="n">
-        <v>-26.85</v>
-      </c>
-      <c r="AG11"/>
-      <c r="AH11"/>
+        <v>-28.58</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>168</v>
+      </c>
       <c r="AI11" t="n">
         <v>360</v>
       </c>
@@ -3071,13 +3192,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s">
         <v>164</v>
@@ -3085,27 +3206,31 @@
       <c r="E12" t="s">
         <v>165</v>
       </c>
-      <c r="F12"/>
-      <c r="G12"/>
+      <c r="F12" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.5</v>
+      </c>
       <c r="H12" s="22"/>
       <c r="I12" s="22"/>
       <c r="J12" s="22" t="n">
-        <v>34.8</v>
+        <v>23</v>
       </c>
       <c r="K12" s="22" t="n">
-        <v>37</v>
+        <v>24.5</v>
       </c>
       <c r="L12" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="M12" t="s">
         <v>167</v>
       </c>
       <c r="N12" t="n">
-        <v>252000000</v>
+        <v>261000000</v>
       </c>
       <c r="O12" t="n">
-        <v>32000000</v>
+        <v>24500000</v>
       </c>
       <c r="P12" t="s">
         <v>168</v>
@@ -3118,10 +3243,10 @@
       </c>
       <c r="S12"/>
       <c r="T12" t="n">
-        <v>0.0000064</v>
+        <v>0.00000606</v>
       </c>
       <c r="U12" t="n">
-        <v>0.00000079</v>
+        <v>0.00000017</v>
       </c>
       <c r="V12" t="s">
         <v>168</v>
@@ -3134,10 +3259,10 @@
       </c>
       <c r="Y12"/>
       <c r="Z12" t="n">
-        <v>0.00001099</v>
+        <v>0.0000218</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.000000555</v>
+        <v>0.0000007</v>
       </c>
       <c r="AB12" t="s">
         <v>168</v>
@@ -3150,10 +3275,14 @@
       </c>
       <c r="AE12"/>
       <c r="AF12" t="n">
-        <v>-26.66</v>
-      </c>
-      <c r="AG12"/>
-      <c r="AH12"/>
+        <v>-27.87</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>168</v>
+      </c>
       <c r="AI12" t="n">
         <v>360</v>
       </c>
@@ -3232,13 +3361,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B13" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
         <v>164</v>
@@ -3246,27 +3375,31 @@
       <c r="E13" t="s">
         <v>165</v>
       </c>
-      <c r="F13"/>
-      <c r="G13"/>
+      <c r="F13" t="n">
+        <v>47</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15.5</v>
+      </c>
       <c r="H13" s="22"/>
       <c r="I13" s="22"/>
       <c r="J13" s="22" t="n">
-        <v>34.8</v>
+        <v>17.2</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>37.5</v>
+        <v>17.6</v>
       </c>
       <c r="L13" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="M13" t="s">
         <v>167</v>
       </c>
       <c r="N13" t="n">
-        <v>274000000</v>
+        <v>298000000</v>
       </c>
       <c r="O13" t="n">
-        <v>4500000</v>
+        <v>39000000</v>
       </c>
       <c r="P13" t="s">
         <v>168</v>
@@ -3279,10 +3412,10 @@
       </c>
       <c r="S13"/>
       <c r="T13" t="n">
-        <v>0.0000064</v>
+        <v>0.00001832</v>
       </c>
       <c r="U13" t="n">
-        <v>0.000000615</v>
+        <v>0.00000142</v>
       </c>
       <c r="V13" t="s">
         <v>168</v>
@@ -3295,10 +3428,10 @@
       </c>
       <c r="Y13"/>
       <c r="Z13" t="n">
-        <v>0.00001082</v>
+        <v>0.0000154</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.000000585</v>
+        <v>0.00000105</v>
       </c>
       <c r="AB13" t="s">
         <v>168</v>
@@ -3311,10 +3444,14 @@
       </c>
       <c r="AE13"/>
       <c r="AF13" t="n">
-        <v>-26.77</v>
-      </c>
-      <c r="AG13"/>
-      <c r="AH13"/>
+        <v>-27.27</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>168</v>
+      </c>
       <c r="AI13" t="n">
         <v>360</v>
       </c>
@@ -3393,13 +3530,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
         <v>164</v>
@@ -3407,27 +3544,31 @@
       <c r="E14" t="s">
         <v>165</v>
       </c>
-      <c r="F14"/>
-      <c r="G14"/>
+      <c r="F14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
       <c r="J14" s="22" t="n">
-        <v>36.4</v>
+        <v>18.5</v>
       </c>
       <c r="K14" s="22" t="n">
-        <v>36.7</v>
+        <v>19.5</v>
       </c>
       <c r="L14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M14" t="s">
         <v>167</v>
       </c>
       <c r="N14" t="n">
-        <v>291000000</v>
+        <v>305000000</v>
       </c>
       <c r="O14" t="n">
-        <v>49500000</v>
+        <v>27500000</v>
       </c>
       <c r="P14" t="s">
         <v>168</v>
@@ -3440,10 +3581,10 @@
       </c>
       <c r="S14"/>
       <c r="T14" t="n">
-        <v>0.00000681</v>
+        <v>0.00000539</v>
       </c>
       <c r="U14" t="n">
-        <v>0.000000645</v>
+        <v>0.000000215</v>
       </c>
       <c r="V14" t="s">
         <v>168</v>
@@ -3456,7 +3597,7 @@
       </c>
       <c r="Y14"/>
       <c r="Z14" t="n">
-        <v>0.0000103</v>
+        <v>0.0000218</v>
       </c>
       <c r="AA14" t="n">
         <v>0.0000007</v>
@@ -3472,10 +3613,14 @@
       </c>
       <c r="AE14"/>
       <c r="AF14" t="n">
-        <v>-26.91</v>
-      </c>
-      <c r="AG14"/>
-      <c r="AH14"/>
+        <v>-25.9</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>168</v>
+      </c>
       <c r="AI14" t="n">
         <v>360</v>
       </c>
@@ -3554,13 +3699,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
         <v>164</v>
@@ -3573,26 +3718,22 @@
       <c r="H15" s="22"/>
       <c r="I15" s="22"/>
       <c r="J15" s="22" t="n">
-        <v>38</v>
+        <v>410.5</v>
       </c>
       <c r="K15" s="22" t="n">
-        <v>38.5</v>
+        <v>412.4</v>
       </c>
       <c r="L15" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="N15" t="n">
-        <v>212000000</v>
-      </c>
-      <c r="O15" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="P15" t="s">
-        <v>168</v>
-      </c>
+        <v>1000000</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
@@ -3601,14 +3742,10 @@
       </c>
       <c r="S15"/>
       <c r="T15" t="n">
-        <v>0.00000653</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.000000705</v>
-      </c>
-      <c r="V15" t="s">
-        <v>168</v>
-      </c>
+        <v>0.000039</v>
+      </c>
+      <c r="U15"/>
+      <c r="V15"/>
       <c r="W15" t="n">
         <v>0</v>
       </c>
@@ -3617,14 +3754,10 @@
       </c>
       <c r="Y15"/>
       <c r="Z15" t="n">
-        <v>0.0000117</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.000000725</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>168</v>
-      </c>
+        <v>0.00003</v>
+      </c>
+      <c r="AA15"/>
+      <c r="AB15"/>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
@@ -3632,9 +3765,7 @@
         <v>0</v>
       </c>
       <c r="AE15"/>
-      <c r="AF15" t="n">
-        <v>-26.83</v>
-      </c>
+      <c r="AF15"/>
       <c r="AG15"/>
       <c r="AH15"/>
       <c r="AI15" t="n">
@@ -3710,18 +3841,18 @@
         <v>170</v>
       </c>
       <c r="BI15" s="1" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D16" t="s">
         <v>164</v>
@@ -3734,26 +3865,22 @@
       <c r="H16" s="22"/>
       <c r="I16" s="22"/>
       <c r="J16" s="22" t="n">
-        <v>38</v>
+        <v>410.5</v>
       </c>
       <c r="K16" s="22" t="n">
-        <v>38.5</v>
+        <v>412.4</v>
       </c>
       <c r="L16" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="N16" t="n">
-        <v>220000000</v>
-      </c>
-      <c r="O16" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="P16" t="s">
-        <v>168</v>
-      </c>
+        <v>1750000</v>
+      </c>
+      <c r="O16"/>
+      <c r="P16"/>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
@@ -3762,14 +3889,10 @@
       </c>
       <c r="S16"/>
       <c r="T16" t="n">
-        <v>0.0000076</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.000000785</v>
-      </c>
-      <c r="V16" t="s">
-        <v>168</v>
-      </c>
+        <v>0.000029</v>
+      </c>
+      <c r="U16"/>
+      <c r="V16"/>
       <c r="W16" t="n">
         <v>0</v>
       </c>
@@ -3778,14 +3901,10 @@
       </c>
       <c r="Y16"/>
       <c r="Z16" t="n">
-        <v>0.000012</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.000000705</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>168</v>
-      </c>
+        <v>0.000015</v>
+      </c>
+      <c r="AA16"/>
+      <c r="AB16"/>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
@@ -3793,9 +3912,7 @@
         <v>0</v>
       </c>
       <c r="AE16"/>
-      <c r="AF16" t="n">
-        <v>-26.69</v>
-      </c>
+      <c r="AF16"/>
       <c r="AG16"/>
       <c r="AH16"/>
       <c r="AI16" t="n">
@@ -3871,7 +3988,7 @@
         <v>170</v>
       </c>
       <c r="BI16" s="1" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
@@ -3879,10 +3996,10 @@
         <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
         <v>164</v>
@@ -3895,26 +4012,22 @@
       <c r="H17" s="22"/>
       <c r="I17" s="22"/>
       <c r="J17" s="22" t="n">
-        <v>23</v>
+        <v>410.5</v>
       </c>
       <c r="K17" s="22" t="n">
-        <v>24.5</v>
+        <v>412.4</v>
       </c>
       <c r="L17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="N17" t="n">
-        <v>89000000</v>
-      </c>
-      <c r="O17" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="P17" t="s">
-        <v>168</v>
-      </c>
+        <v>3350000</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
@@ -3923,14 +4036,10 @@
       </c>
       <c r="S17"/>
       <c r="T17" t="n">
-        <v>0.00001376</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.00000159</v>
-      </c>
-      <c r="V17" t="s">
-        <v>168</v>
-      </c>
+        <v>0.000021</v>
+      </c>
+      <c r="U17"/>
+      <c r="V17"/>
       <c r="W17" t="n">
         <v>0</v>
       </c>
@@ -3939,14 +4048,10 @@
       </c>
       <c r="Y17"/>
       <c r="Z17" t="n">
-        <v>0.00001754</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.00000097</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>168</v>
-      </c>
+        <v>0.00003</v>
+      </c>
+      <c r="AA17"/>
+      <c r="AB17"/>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
@@ -3954,15 +4059,9 @@
         <v>0</v>
       </c>
       <c r="AE17"/>
-      <c r="AF17" t="n">
-        <v>-27.17</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>168</v>
-      </c>
+      <c r="AF17"/>
+      <c r="AG17"/>
+      <c r="AH17"/>
       <c r="AI17" t="n">
         <v>360</v>
       </c>
@@ -4036,46 +4135,50 @@
         <v>170</v>
       </c>
       <c r="BI17" s="1" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D18" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E18" t="s">
-        <v>165</v>
-      </c>
-      <c r="F18"/>
-      <c r="G18"/>
+        <v>203</v>
+      </c>
+      <c r="F18" t="n">
+        <v>47.5333333333333</v>
+      </c>
+      <c r="G18" t="n">
+        <v>19.0333333333333</v>
+      </c>
       <c r="H18" s="22"/>
       <c r="I18" s="22"/>
       <c r="J18" s="22" t="n">
-        <v>24.5</v>
+        <v>27</v>
       </c>
       <c r="K18" s="22" t="n">
-        <v>25.5</v>
+        <v>32</v>
       </c>
       <c r="L18" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="M18" t="s">
         <v>167</v>
       </c>
       <c r="N18" t="n">
-        <v>105000000</v>
+        <v>646000000</v>
       </c>
       <c r="O18" t="n">
-        <v>14000000</v>
+        <v>39375000</v>
       </c>
       <c r="P18" t="s">
         <v>168</v>
@@ -4088,10 +4191,10 @@
       </c>
       <c r="S18"/>
       <c r="T18" t="n">
-        <v>0.00001266</v>
+        <v>0.00000295</v>
       </c>
       <c r="U18" t="n">
-        <v>0.000001145</v>
+        <v>0.00000018</v>
       </c>
       <c r="V18" t="s">
         <v>168</v>
@@ -4104,14 +4207,10 @@
       </c>
       <c r="Y18"/>
       <c r="Z18" t="n">
-        <v>0.00001501</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.000000875</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>168</v>
-      </c>
+        <v>0.00001</v>
+      </c>
+      <c r="AA18"/>
+      <c r="AB18"/>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
@@ -4120,10 +4219,10 @@
       </c>
       <c r="AE18"/>
       <c r="AF18" t="n">
-        <v>-26.95</v>
+        <v>-28.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="AH18" t="s">
         <v>168</v>
@@ -4206,41 +4305,45 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C19" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D19" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
-      </c>
-      <c r="F19"/>
-      <c r="G19"/>
+        <v>203</v>
+      </c>
+      <c r="F19" t="n">
+        <v>47.5333333333333</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19.0333333333333</v>
+      </c>
       <c r="H19" s="22"/>
       <c r="I19" s="22"/>
       <c r="J19" s="22" t="n">
-        <v>24.5</v>
+        <v>27</v>
       </c>
       <c r="K19" s="22" t="n">
-        <v>25.5</v>
+        <v>32</v>
       </c>
       <c r="L19" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s">
         <v>167</v>
       </c>
       <c r="N19" t="n">
-        <v>104000000</v>
+        <v>646000000</v>
       </c>
       <c r="O19" t="n">
-        <v>12500000</v>
+        <v>53000000</v>
       </c>
       <c r="P19" t="s">
         <v>168</v>
@@ -4253,10 +4356,10 @@
       </c>
       <c r="S19"/>
       <c r="T19" t="n">
-        <v>0.00001125</v>
+        <v>0.00000331</v>
       </c>
       <c r="U19" t="n">
-        <v>0.00000114</v>
+        <v>0.00000042</v>
       </c>
       <c r="V19" t="s">
         <v>168</v>
@@ -4269,14 +4372,10 @@
       </c>
       <c r="Y19"/>
       <c r="Z19" t="n">
-        <v>0.00001538</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.000000835</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>168</v>
-      </c>
+        <v>0.00001</v>
+      </c>
+      <c r="AA19"/>
+      <c r="AB19"/>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
@@ -4285,10 +4384,10 @@
       </c>
       <c r="AE19"/>
       <c r="AF19" t="n">
-        <v>-26.68</v>
+        <v>-28.54</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="AH19" t="s">
         <v>168</v>
@@ -4371,41 +4470,45 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s">
         <v>200</v>
       </c>
-      <c r="B20" t="s">
-        <v>185</v>
-      </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D20" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
-      </c>
-      <c r="F20"/>
-      <c r="G20"/>
+        <v>203</v>
+      </c>
+      <c r="F20" t="n">
+        <v>45.9833333333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14.1666666666667</v>
+      </c>
       <c r="H20" s="22"/>
       <c r="I20" s="22"/>
       <c r="J20" s="22" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="K20" s="22" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L20" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s">
         <v>167</v>
       </c>
       <c r="N20" t="n">
-        <v>78000000</v>
+        <v>700000000</v>
       </c>
       <c r="O20" t="n">
-        <v>4500000</v>
+        <v>79000000</v>
       </c>
       <c r="P20" t="s">
         <v>168</v>
@@ -4418,10 +4521,10 @@
       </c>
       <c r="S20"/>
       <c r="T20" t="n">
-        <v>0.00001287</v>
+        <v>0.00000325</v>
       </c>
       <c r="U20" t="n">
-        <v>0.000001315</v>
+        <v>0.000000725</v>
       </c>
       <c r="V20" t="s">
         <v>168</v>
@@ -4434,14 +4537,10 @@
       </c>
       <c r="Y20"/>
       <c r="Z20" t="n">
-        <v>0.00001797</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.000001085</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>168</v>
-      </c>
+        <v>0.00001</v>
+      </c>
+      <c r="AA20"/>
+      <c r="AB20"/>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
@@ -4450,10 +4549,10 @@
       </c>
       <c r="AE20"/>
       <c r="AF20" t="n">
-        <v>-26.35</v>
+        <v>-28.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.37</v>
+        <v>0.07</v>
       </c>
       <c r="AH20" t="s">
         <v>168</v>
@@ -4536,41 +4635,45 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C21" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
-      </c>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="K21" s="22" t="n">
-        <v>31.4</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F21" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="H21" s="22" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I21" s="22" t="n">
+        <v>0.199999999999996</v>
+      </c>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
       <c r="L21" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s">
         <v>167</v>
       </c>
       <c r="N21" t="n">
-        <v>112000000</v>
+        <v>282000000</v>
       </c>
       <c r="O21" t="n">
-        <v>15000000</v>
+        <v>29500000</v>
       </c>
       <c r="P21" t="s">
         <v>168</v>
@@ -4583,10 +4686,10 @@
       </c>
       <c r="S21"/>
       <c r="T21" t="n">
-        <v>0.00001341</v>
+        <v>0.00000756</v>
       </c>
       <c r="U21" t="n">
-        <v>0.000001235</v>
+        <v>0.000001</v>
       </c>
       <c r="V21" t="s">
         <v>168</v>
@@ -4599,10 +4702,10 @@
       </c>
       <c r="Y21"/>
       <c r="Z21" t="n">
-        <v>0.00001637</v>
+        <v>0.0000132</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.00000097</v>
+        <v>0.00000065</v>
       </c>
       <c r="AB21" t="s">
         <v>168</v>
@@ -4615,10 +4718,10 @@
       </c>
       <c r="AE21"/>
       <c r="AF21" t="n">
-        <v>-26.44</v>
+        <v>-27.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="AH21" t="s">
         <v>168</v>
@@ -4701,41 +4804,45 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" t="s">
         <v>203</v>
       </c>
-      <c r="B22" t="s">
-        <v>185</v>
-      </c>
-      <c r="C22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="K22" s="22" t="n">
-        <v>32.4</v>
-      </c>
+      <c r="F22" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="H22" s="22" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I22" s="22" t="n">
+        <v>0.199999999999996</v>
+      </c>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
       <c r="L22" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s">
         <v>167</v>
       </c>
       <c r="N22" t="n">
-        <v>69000000</v>
+        <v>410000000</v>
       </c>
       <c r="O22" t="n">
-        <v>5500000</v>
+        <v>32500000</v>
       </c>
       <c r="P22" t="s">
         <v>168</v>
@@ -4748,10 +4855,10 @@
       </c>
       <c r="S22"/>
       <c r="T22" t="n">
-        <v>0.00001429</v>
+        <v>0.00000712</v>
       </c>
       <c r="U22" t="n">
-        <v>0.000001575</v>
+        <v>0.00000075</v>
       </c>
       <c r="V22" t="s">
         <v>168</v>
@@ -4764,10 +4871,10 @@
       </c>
       <c r="Y22"/>
       <c r="Z22" t="n">
-        <v>0.00001893</v>
+        <v>0.0000218</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.00000091</v>
+        <v>0.0000007</v>
       </c>
       <c r="AB22" t="s">
         <v>168</v>
@@ -4780,10 +4887,10 @@
       </c>
       <c r="AE22"/>
       <c r="AF22" t="n">
-        <v>-25.33</v>
+        <v>-28.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.345</v>
+        <v>0.4</v>
       </c>
       <c r="AH22" t="s">
         <v>168</v>
@@ -4866,41 +4973,45 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C23" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="K23" s="22" t="n">
-        <v>33.9</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F23" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="H23" s="22" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I23" s="22" t="n">
+        <v>0.199999999999996</v>
+      </c>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
       <c r="L23" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s">
         <v>167</v>
       </c>
       <c r="N23" t="n">
-        <v>96000000</v>
+        <v>327000000</v>
       </c>
       <c r="O23" t="n">
-        <v>13000000</v>
+        <v>23000000</v>
       </c>
       <c r="P23" t="s">
         <v>168</v>
@@ -4913,10 +5024,10 @@
       </c>
       <c r="S23"/>
       <c r="T23" t="n">
-        <v>0.00001316</v>
+        <v>0.00000629</v>
       </c>
       <c r="U23" t="n">
-        <v>0.00000134</v>
+        <v>0.00000065</v>
       </c>
       <c r="V23" t="s">
         <v>168</v>
@@ -4929,10 +5040,10 @@
       </c>
       <c r="Y23"/>
       <c r="Z23" t="n">
-        <v>0.00001719</v>
+        <v>0.0000163</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.0000008</v>
+        <v>0.0000005</v>
       </c>
       <c r="AB23" t="s">
         <v>168</v>
@@ -4945,10 +5056,10 @@
       </c>
       <c r="AE23"/>
       <c r="AF23" t="n">
-        <v>-25.78</v>
+        <v>-29.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="AH23" t="s">
         <v>168</v>
@@ -5031,45 +5142,41 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C24" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D24" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
-      </c>
-      <c r="F24" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="G24" t="n">
-        <v>12.36</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F24"/>
+      <c r="G24"/>
       <c r="H24" s="22"/>
       <c r="I24" s="22"/>
       <c r="J24" s="22" t="n">
-        <v>33</v>
+        <v>35.4</v>
       </c>
       <c r="K24" s="22" t="n">
-        <v>33.9</v>
+        <v>35.8</v>
       </c>
       <c r="L24" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s">
         <v>167</v>
       </c>
       <c r="N24" t="n">
-        <v>81000000</v>
+        <v>259000000</v>
       </c>
       <c r="O24" t="n">
-        <v>11500000</v>
+        <v>55000000</v>
       </c>
       <c r="P24" t="s">
         <v>168</v>
@@ -5082,10 +5189,10 @@
       </c>
       <c r="S24"/>
       <c r="T24" t="n">
-        <v>0.0000141</v>
+        <v>0.0000075</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0000007</v>
+        <v>0.00000085</v>
       </c>
       <c r="V24" t="s">
         <v>168</v>
@@ -5098,10 +5205,10 @@
       </c>
       <c r="Y24"/>
       <c r="Z24" t="n">
-        <v>0.0000171</v>
+        <v>0.00001165</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.00000065</v>
+        <v>0.00000075</v>
       </c>
       <c r="AB24" t="s">
         <v>168</v>
@@ -5114,14 +5221,10 @@
       </c>
       <c r="AE24"/>
       <c r="AF24" t="n">
-        <v>-25.87</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>168</v>
-      </c>
+        <v>-27.37</v>
+      </c>
+      <c r="AG24"/>
+      <c r="AH24"/>
       <c r="AI24" t="n">
         <v>360</v>
       </c>
@@ -5200,45 +5303,41 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C25" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>165</v>
-      </c>
-      <c r="F25" t="n">
-        <v>51.27</v>
-      </c>
-      <c r="G25" t="n">
-        <v>14.59</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F25"/>
+      <c r="G25"/>
       <c r="H25" s="22"/>
       <c r="I25" s="22"/>
       <c r="J25" s="22" t="n">
-        <v>26</v>
+        <v>36.2</v>
       </c>
       <c r="K25" s="22" t="n">
-        <v>27</v>
+        <v>36.4</v>
       </c>
       <c r="L25" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="M25" t="s">
         <v>167</v>
       </c>
       <c r="N25" t="n">
-        <v>105000000</v>
+        <v>299000000</v>
       </c>
       <c r="O25" t="n">
-        <v>25500000</v>
+        <v>48000000</v>
       </c>
       <c r="P25" t="s">
         <v>168</v>
@@ -5251,10 +5350,10 @@
       </c>
       <c r="S25"/>
       <c r="T25" t="n">
-        <v>0.0000142</v>
+        <v>0.00000683</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0000011</v>
+        <v>0.00000064</v>
       </c>
       <c r="V25" t="s">
         <v>168</v>
@@ -5267,10 +5366,10 @@
       </c>
       <c r="Y25"/>
       <c r="Z25" t="n">
-        <v>0.0000144</v>
+        <v>0.00001103</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.00000115</v>
+        <v>0.000000665</v>
       </c>
       <c r="AB25" t="s">
         <v>168</v>
@@ -5283,14 +5382,10 @@
       </c>
       <c r="AE25"/>
       <c r="AF25" t="n">
-        <v>-27.09</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>168</v>
-      </c>
+        <v>-26.85</v>
+      </c>
+      <c r="AG25"/>
+      <c r="AH25"/>
       <c r="AI25" t="n">
         <v>360</v>
       </c>
@@ -5369,45 +5464,41 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B26" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C26" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
-      </c>
-      <c r="F26" t="n">
-        <v>51.12</v>
-      </c>
-      <c r="G26" t="n">
-        <v>12.54</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F26"/>
+      <c r="G26"/>
       <c r="H26" s="22"/>
       <c r="I26" s="22"/>
       <c r="J26" s="22" t="n">
-        <v>24.5</v>
+        <v>34.8</v>
       </c>
       <c r="K26" s="22" t="n">
-        <v>25.5</v>
+        <v>37</v>
       </c>
       <c r="L26" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="M26" t="s">
         <v>167</v>
       </c>
       <c r="N26" t="n">
-        <v>100000000</v>
+        <v>252000000</v>
       </c>
       <c r="O26" t="n">
-        <v>16000000</v>
+        <v>32000000</v>
       </c>
       <c r="P26" t="s">
         <v>168</v>
@@ -5420,10 +5511,10 @@
       </c>
       <c r="S26"/>
       <c r="T26" t="n">
-        <v>0.0000148</v>
+        <v>0.0000064</v>
       </c>
       <c r="U26" t="n">
-        <v>0.00000085</v>
+        <v>0.00000079</v>
       </c>
       <c r="V26" t="s">
         <v>168</v>
@@ -5436,10 +5527,10 @@
       </c>
       <c r="Y26"/>
       <c r="Z26" t="n">
-        <v>0.0000137</v>
+        <v>0.00001099</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.00000075</v>
+        <v>0.000000555</v>
       </c>
       <c r="AB26" t="s">
         <v>168</v>
@@ -5452,14 +5543,10 @@
       </c>
       <c r="AE26"/>
       <c r="AF26" t="n">
-        <v>-26.95</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>168</v>
-      </c>
+        <v>-26.66</v>
+      </c>
+      <c r="AG26"/>
+      <c r="AH26"/>
       <c r="AI26" t="n">
         <v>360</v>
       </c>
@@ -5538,45 +5625,41 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B27" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D27" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>165</v>
-      </c>
-      <c r="F27" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="G27" t="n">
-        <v>12.31</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F27"/>
+      <c r="G27"/>
       <c r="H27" s="22"/>
       <c r="I27" s="22"/>
       <c r="J27" s="22" t="n">
-        <v>23</v>
+        <v>34.8</v>
       </c>
       <c r="K27" s="22" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="L27" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="M27" t="s">
         <v>167</v>
       </c>
       <c r="N27" t="n">
-        <v>94000000</v>
+        <v>274000000</v>
       </c>
       <c r="O27" t="n">
-        <v>6500000</v>
+        <v>4500000</v>
       </c>
       <c r="P27" t="s">
         <v>168</v>
@@ -5589,10 +5672,10 @@
       </c>
       <c r="S27"/>
       <c r="T27" t="n">
-        <v>0.0000136</v>
+        <v>0.0000064</v>
       </c>
       <c r="U27" t="n">
-        <v>0.00000035</v>
+        <v>0.000000615</v>
       </c>
       <c r="V27" t="s">
         <v>168</v>
@@ -5605,10 +5688,10 @@
       </c>
       <c r="Y27"/>
       <c r="Z27" t="n">
-        <v>0.000016</v>
+        <v>0.00001082</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.0000005</v>
+        <v>0.000000585</v>
       </c>
       <c r="AB27" t="s">
         <v>168</v>
@@ -5621,14 +5704,10 @@
       </c>
       <c r="AE27"/>
       <c r="AF27" t="n">
-        <v>-27.22</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>168</v>
-      </c>
+        <v>-26.77</v>
+      </c>
+      <c r="AG27"/>
+      <c r="AH27"/>
       <c r="AI27" t="n">
         <v>360</v>
       </c>
@@ -5707,45 +5786,41 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B28" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C28" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D28" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>165</v>
-      </c>
-      <c r="F28" t="n">
-        <v>51.17</v>
-      </c>
-      <c r="G28" t="n">
-        <v>12.5</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F28"/>
+      <c r="G28"/>
       <c r="H28" s="22"/>
       <c r="I28" s="22"/>
       <c r="J28" s="22" t="n">
-        <v>23</v>
+        <v>36.4</v>
       </c>
       <c r="K28" s="22" t="n">
-        <v>24.5</v>
+        <v>36.7</v>
       </c>
       <c r="L28" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="M28" t="s">
         <v>167</v>
       </c>
       <c r="N28" t="n">
-        <v>97000000</v>
+        <v>291000000</v>
       </c>
       <c r="O28" t="n">
-        <v>14000000</v>
+        <v>49500000</v>
       </c>
       <c r="P28" t="s">
         <v>168</v>
@@ -5758,10 +5833,10 @@
       </c>
       <c r="S28"/>
       <c r="T28" t="n">
-        <v>0.0000143</v>
+        <v>0.00000681</v>
       </c>
       <c r="U28" t="n">
-        <v>0.00000055</v>
+        <v>0.000000645</v>
       </c>
       <c r="V28" t="s">
         <v>168</v>
@@ -5774,7 +5849,7 @@
       </c>
       <c r="Y28"/>
       <c r="Z28" t="n">
-        <v>0.0000141</v>
+        <v>0.0000103</v>
       </c>
       <c r="AA28" t="n">
         <v>0.0000007</v>
@@ -5790,14 +5865,10 @@
       </c>
       <c r="AE28"/>
       <c r="AF28" t="n">
-        <v>-27.24</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>168</v>
-      </c>
+        <v>-26.91</v>
+      </c>
+      <c r="AG28"/>
+      <c r="AH28"/>
       <c r="AI28" t="n">
         <v>360</v>
       </c>
@@ -5875,123 +5946,2833 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="s">
+        <v>224</v>
+      </c>
+      <c r="B29" t="s">
+        <v>215</v>
+      </c>
+      <c r="C29" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" t="s">
+        <v>202</v>
+      </c>
+      <c r="E29" t="s">
+        <v>203</v>
+      </c>
+      <c r="F29"/>
+      <c r="G29"/>
       <c r="H29" s="22"/>
       <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="BI29" s="1"/>
+      <c r="J29" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="K29" s="22" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="L29" t="s">
+        <v>225</v>
+      </c>
+      <c r="M29" t="s">
+        <v>167</v>
+      </c>
+      <c r="N29" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="O29" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="P29" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29"/>
+      <c r="T29" t="n">
+        <v>0.00000653</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.000000705</v>
+      </c>
+      <c r="V29" t="s">
+        <v>168</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29"/>
+      <c r="Z29" t="n">
+        <v>0.0000117</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.000000725</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29"/>
+      <c r="AF29" t="n">
+        <v>-26.83</v>
+      </c>
+      <c r="AG29"/>
+      <c r="AH29"/>
+      <c r="AI29" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK29"/>
+      <c r="AL29"/>
+      <c r="AM29"/>
+      <c r="AN29" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP29" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB29" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE29" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH29" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI29" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="30">
+      <c r="A30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" t="s">
+        <v>216</v>
+      </c>
+      <c r="D30" t="s">
+        <v>202</v>
+      </c>
+      <c r="E30" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30"/>
+      <c r="G30"/>
       <c r="H30" s="22"/>
       <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="BI30" s="1"/>
+      <c r="J30" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="K30" s="22" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="L30" t="s">
+        <v>225</v>
+      </c>
+      <c r="M30" t="s">
+        <v>167</v>
+      </c>
+      <c r="N30" t="n">
+        <v>220000000</v>
+      </c>
+      <c r="O30" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="P30" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30"/>
+      <c r="T30" t="n">
+        <v>0.0000076</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.000000785</v>
+      </c>
+      <c r="V30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30"/>
+      <c r="Z30" t="n">
+        <v>0.000012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.000000705</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30"/>
+      <c r="AF30" t="n">
+        <v>-26.69</v>
+      </c>
+      <c r="AG30"/>
+      <c r="AH30"/>
+      <c r="AI30" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK30"/>
+      <c r="AL30"/>
+      <c r="AM30"/>
+      <c r="AN30" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB30" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE30" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH30" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI30" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="31">
+      <c r="A31" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" t="s">
+        <v>203</v>
+      </c>
+      <c r="F31"/>
+      <c r="G31"/>
       <c r="H31" s="22"/>
       <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="BI31" s="1"/>
+      <c r="J31" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="K31" s="22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L31" t="s">
+        <v>225</v>
+      </c>
+      <c r="M31" t="s">
+        <v>167</v>
+      </c>
+      <c r="N31" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="O31" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="P31" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31"/>
+      <c r="T31" t="n">
+        <v>0.00001376</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.00000159</v>
+      </c>
+      <c r="V31" t="s">
+        <v>168</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31"/>
+      <c r="Z31" t="n">
+        <v>0.00001754</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.00000097</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31"/>
+      <c r="AF31" t="n">
+        <v>-27.17</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK31"/>
+      <c r="AL31"/>
+      <c r="AM31"/>
+      <c r="AN31" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP31" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS31" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB31" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE31" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH31" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI31" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="32">
+      <c r="A32" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32" t="s">
+        <v>203</v>
+      </c>
+      <c r="F32"/>
+      <c r="G32"/>
       <c r="H32" s="22"/>
       <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="BI32" s="1"/>
+      <c r="J32" s="22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K32" s="22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L32" t="s">
+        <v>225</v>
+      </c>
+      <c r="M32" t="s">
+        <v>167</v>
+      </c>
+      <c r="N32" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="O32" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="P32" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32"/>
+      <c r="T32" t="n">
+        <v>0.00001266</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.000001145</v>
+      </c>
+      <c r="V32" t="s">
+        <v>168</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32"/>
+      <c r="Z32" t="n">
+        <v>0.00001501</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.000000875</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32"/>
+      <c r="AF32" t="n">
+        <v>-26.95</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK32"/>
+      <c r="AL32"/>
+      <c r="AM32"/>
+      <c r="AN32" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP32" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS32" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB32" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE32" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH32" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI32" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="33">
+      <c r="A33" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" t="s">
+        <v>215</v>
+      </c>
+      <c r="C33" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33"/>
+      <c r="G33"/>
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="BI33" s="1"/>
+      <c r="J33" s="22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K33" s="22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L33" t="s">
+        <v>225</v>
+      </c>
+      <c r="M33" t="s">
+        <v>167</v>
+      </c>
+      <c r="N33" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="O33" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="P33" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33"/>
+      <c r="T33" t="n">
+        <v>0.00001125</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.00000114</v>
+      </c>
+      <c r="V33" t="s">
+        <v>168</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33"/>
+      <c r="Z33" t="n">
+        <v>0.00001538</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.000000835</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33"/>
+      <c r="AF33" t="n">
+        <v>-26.68</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK33"/>
+      <c r="AL33"/>
+      <c r="AM33"/>
+      <c r="AN33" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP33" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS33" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB33" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE33" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH33" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI33" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="34">
+      <c r="A34" t="s">
+        <v>230</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" t="s">
+        <v>202</v>
+      </c>
+      <c r="E34" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34"/>
+      <c r="G34"/>
       <c r="H34" s="22"/>
       <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="BI34" s="1"/>
+      <c r="J34" s="22" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="K34" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="L34" t="s">
+        <v>225</v>
+      </c>
+      <c r="M34" t="s">
+        <v>167</v>
+      </c>
+      <c r="N34" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="P34" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34"/>
+      <c r="T34" t="n">
+        <v>0.00001287</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.000001315</v>
+      </c>
+      <c r="V34" t="s">
+        <v>168</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34"/>
+      <c r="Z34" t="n">
+        <v>0.00001797</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.000001085</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34"/>
+      <c r="AF34" t="n">
+        <v>-26.35</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK34"/>
+      <c r="AL34"/>
+      <c r="AM34"/>
+      <c r="AN34" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP34" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS34" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB34" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE34" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH34" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI34" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="35">
+      <c r="A35" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" t="s">
+        <v>216</v>
+      </c>
+      <c r="D35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35"/>
+      <c r="G35"/>
       <c r="H35" s="22"/>
       <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="BI35" s="1"/>
+      <c r="J35" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="K35" s="22" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="L35" t="s">
+        <v>232</v>
+      </c>
+      <c r="M35" t="s">
+        <v>167</v>
+      </c>
+      <c r="N35" t="n">
+        <v>112000000</v>
+      </c>
+      <c r="O35" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="P35" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35"/>
+      <c r="T35" t="n">
+        <v>0.00001341</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.000001235</v>
+      </c>
+      <c r="V35" t="s">
+        <v>168</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35"/>
+      <c r="Z35" t="n">
+        <v>0.00001637</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.00000097</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35"/>
+      <c r="AF35" t="n">
+        <v>-26.44</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK35"/>
+      <c r="AL35"/>
+      <c r="AM35"/>
+      <c r="AN35" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS35" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB35" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE35" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH35" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI35" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="36">
+      <c r="A36" t="s">
+        <v>233</v>
+      </c>
+      <c r="B36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" t="s">
+        <v>202</v>
+      </c>
+      <c r="E36" t="s">
+        <v>203</v>
+      </c>
+      <c r="F36"/>
+      <c r="G36"/>
       <c r="H36" s="22"/>
       <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="BI36" s="1"/>
+      <c r="J36" s="22" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="K36" s="22" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="L36" t="s">
+        <v>225</v>
+      </c>
+      <c r="M36" t="s">
+        <v>167</v>
+      </c>
+      <c r="N36" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="O36" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="P36" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36"/>
+      <c r="T36" t="n">
+        <v>0.00001429</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.000001575</v>
+      </c>
+      <c r="V36" t="s">
+        <v>168</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36"/>
+      <c r="Z36" t="n">
+        <v>0.00001893</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.00000091</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36"/>
+      <c r="AF36" t="n">
+        <v>-25.33</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK36"/>
+      <c r="AL36"/>
+      <c r="AM36"/>
+      <c r="AN36" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS36" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB36" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE36" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH36" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI36" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="37">
+      <c r="A37" t="s">
+        <v>234</v>
+      </c>
+      <c r="B37" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" t="s">
+        <v>203</v>
+      </c>
+      <c r="F37"/>
+      <c r="G37"/>
       <c r="H37" s="22"/>
       <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="BI37" s="1"/>
+      <c r="J37" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="K37" s="22" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="L37" t="s">
+        <v>225</v>
+      </c>
+      <c r="M37" t="s">
+        <v>167</v>
+      </c>
+      <c r="N37" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O37" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="P37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37"/>
+      <c r="T37" t="n">
+        <v>0.00001316</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.00000134</v>
+      </c>
+      <c r="V37" t="s">
+        <v>168</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37"/>
+      <c r="Z37" t="n">
+        <v>0.00001719</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.0000008</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37"/>
+      <c r="AF37" t="n">
+        <v>-25.78</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK37"/>
+      <c r="AL37"/>
+      <c r="AM37"/>
+      <c r="AN37" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS37" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB37" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE37" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH37" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI37" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="38">
+      <c r="A38" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" t="s">
+        <v>236</v>
+      </c>
+      <c r="C38" t="s">
+        <v>237</v>
+      </c>
+      <c r="D38" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="G38" t="n">
+        <v>12.36</v>
+      </c>
       <c r="H38" s="22"/>
       <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="BI38" s="1"/>
+      <c r="J38" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="K38" s="22" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="L38" t="s">
+        <v>238</v>
+      </c>
+      <c r="M38" t="s">
+        <v>167</v>
+      </c>
+      <c r="N38" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="O38" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="P38" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38"/>
+      <c r="T38" t="n">
+        <v>0.0000141</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.0000007</v>
+      </c>
+      <c r="V38" t="s">
+        <v>168</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38"/>
+      <c r="Z38" t="n">
+        <v>0.0000171</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.00000065</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38"/>
+      <c r="AF38" t="n">
+        <v>-25.87</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK38"/>
+      <c r="AL38"/>
+      <c r="AM38"/>
+      <c r="AN38" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP38" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS38" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB38" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE38" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH38" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI38" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="39">
+      <c r="A39" t="s">
+        <v>239</v>
+      </c>
+      <c r="B39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C39" t="s">
+        <v>237</v>
+      </c>
+      <c r="D39" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" t="s">
+        <v>203</v>
+      </c>
+      <c r="F39" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="G39" t="n">
+        <v>14.59</v>
+      </c>
       <c r="H39" s="22"/>
       <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="BI39" s="1"/>
+      <c r="J39" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="K39" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="L39" t="s">
+        <v>238</v>
+      </c>
+      <c r="M39" t="s">
+        <v>167</v>
+      </c>
+      <c r="N39" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="O39" t="n">
+        <v>25500000</v>
+      </c>
+      <c r="P39" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39"/>
+      <c r="T39" t="n">
+        <v>0.0000142</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.0000011</v>
+      </c>
+      <c r="V39" t="s">
+        <v>168</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39"/>
+      <c r="Z39" t="n">
+        <v>0.0000144</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.00000115</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39"/>
+      <c r="AF39" t="n">
+        <v>-27.09</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK39"/>
+      <c r="AL39"/>
+      <c r="AM39"/>
+      <c r="AN39" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP39" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS39" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB39" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE39" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH39" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI39" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="40">
+      <c r="A40" t="s">
+        <v>240</v>
+      </c>
+      <c r="B40" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" t="s">
+        <v>237</v>
+      </c>
+      <c r="D40" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="G40" t="n">
+        <v>12.54</v>
+      </c>
       <c r="H40" s="22"/>
       <c r="I40" s="22"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="22"/>
-      <c r="BI40" s="1"/>
+      <c r="J40" s="22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K40" s="22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="L40" t="s">
+        <v>238</v>
+      </c>
+      <c r="M40" t="s">
+        <v>167</v>
+      </c>
+      <c r="N40" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O40" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="P40" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40"/>
+      <c r="T40" t="n">
+        <v>0.0000148</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.00000085</v>
+      </c>
+      <c r="V40" t="s">
+        <v>168</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40"/>
+      <c r="Z40" t="n">
+        <v>0.0000137</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.00000075</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40"/>
+      <c r="AF40" t="n">
+        <v>-26.95</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK40"/>
+      <c r="AL40"/>
+      <c r="AM40"/>
+      <c r="AN40" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP40" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS40" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB40" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE40" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH40" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI40" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="41">
+      <c r="A41" t="s">
+        <v>241</v>
+      </c>
+      <c r="B41" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" t="s">
+        <v>237</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" t="n">
+        <v>51.48</v>
+      </c>
+      <c r="G41" t="n">
+        <v>12.31</v>
+      </c>
       <c r="H41" s="22"/>
       <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="BI41" s="1"/>
+      <c r="J41" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="L41" t="s">
+        <v>238</v>
+      </c>
+      <c r="M41" t="s">
+        <v>167</v>
+      </c>
+      <c r="N41" t="n">
+        <v>94000000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="P41" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41"/>
+      <c r="T41" t="n">
+        <v>0.0000136</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.00000035</v>
+      </c>
+      <c r="V41" t="s">
+        <v>168</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41"/>
+      <c r="Z41" t="n">
+        <v>0.000016</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.0000005</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41"/>
+      <c r="AF41" t="n">
+        <v>-27.22</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK41"/>
+      <c r="AL41"/>
+      <c r="AM41"/>
+      <c r="AN41" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP41" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS41" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB41" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE41" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH41" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI41" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="42">
+      <c r="A42" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" t="s">
+        <v>237</v>
+      </c>
+      <c r="D42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="G42" t="n">
+        <v>12.5</v>
+      </c>
       <c r="H42" s="22"/>
       <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="BI42" s="1"/>
+      <c r="J42" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="K42" s="22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L42" t="s">
+        <v>238</v>
+      </c>
+      <c r="M42" t="s">
+        <v>167</v>
+      </c>
+      <c r="N42" t="n">
+        <v>97000000</v>
+      </c>
+      <c r="O42" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="P42" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42"/>
+      <c r="T42" t="n">
+        <v>0.0000143</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.00000055</v>
+      </c>
+      <c r="V42" t="s">
+        <v>168</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42"/>
+      <c r="Z42" t="n">
+        <v>0.0000141</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.0000007</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42"/>
+      <c r="AF42" t="n">
+        <v>-27.24</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK42"/>
+      <c r="AL42"/>
+      <c r="AM42"/>
+      <c r="AN42" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP42" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS42" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB42" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE42" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH42" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI42" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="43">
+      <c r="A43" t="s">
+        <v>243</v>
+      </c>
+      <c r="B43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43" t="s">
+        <v>245</v>
+      </c>
+      <c r="D43" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="G43" t="n">
+        <v>107.016666666667</v>
+      </c>
       <c r="H43" s="22"/>
       <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="BI43" s="1"/>
+      <c r="J43" s="22" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="K43" s="22" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="L43" t="s">
+        <v>246</v>
+      </c>
+      <c r="M43" t="s">
+        <v>167</v>
+      </c>
+      <c r="N43" t="n">
+        <v>136000000</v>
+      </c>
+      <c r="O43" t="n">
+        <v>21500000</v>
+      </c>
+      <c r="P43" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43"/>
+      <c r="T43" t="n">
+        <v>0.0000164</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.0000013</v>
+      </c>
+      <c r="V43" t="s">
+        <v>168</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43"/>
+      <c r="Z43" t="n">
+        <v>0.0000116</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.0000012</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43"/>
+      <c r="AF43" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK43"/>
+      <c r="AL43"/>
+      <c r="AM43"/>
+      <c r="AN43" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP43" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS43" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB43" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE43" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH43" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI43" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="44">
+      <c r="A44" t="s">
+        <v>243</v>
+      </c>
+      <c r="B44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C44" t="s">
+        <v>245</v>
+      </c>
+      <c r="D44" t="s">
+        <v>202</v>
+      </c>
+      <c r="E44" t="s">
+        <v>203</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="G44" t="n">
+        <v>107.016666666667</v>
+      </c>
       <c r="H44" s="22"/>
       <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="BI44" s="1"/>
+      <c r="J44" s="22" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="K44" s="22" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="L44" t="s">
+        <v>246</v>
+      </c>
+      <c r="M44" t="s">
+        <v>167</v>
+      </c>
+      <c r="N44" t="n">
+        <v>417000000</v>
+      </c>
+      <c r="O44" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="P44" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44"/>
+      <c r="T44" t="n">
+        <v>0.0000182</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.00000155</v>
+      </c>
+      <c r="V44" t="s">
+        <v>168</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44"/>
+      <c r="Z44" t="n">
+        <v>0.0000113</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.00000125</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44"/>
+      <c r="AF44" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK44"/>
+      <c r="AL44"/>
+      <c r="AM44"/>
+      <c r="AN44" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP44" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS44" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB44" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE44" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH44" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI44" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="45">
+      <c r="A45" t="s">
+        <v>247</v>
+      </c>
+      <c r="B45" t="s">
+        <v>244</v>
+      </c>
+      <c r="C45" t="s">
+        <v>245</v>
+      </c>
+      <c r="D45" t="s">
+        <v>202</v>
+      </c>
+      <c r="E45" t="s">
+        <v>203</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="G45" t="n">
+        <v>107.016666666667</v>
+      </c>
       <c r="H45" s="22"/>
       <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="BI45" s="1"/>
+      <c r="J45" s="22" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="K45" s="22" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="L45" t="s">
+        <v>246</v>
+      </c>
+      <c r="M45" t="s">
+        <v>167</v>
+      </c>
+      <c r="N45" t="n">
+        <v>399000000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>14500000</v>
+      </c>
+      <c r="P45" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45"/>
+      <c r="T45" t="n">
+        <v>0.0000122</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.00000045</v>
+      </c>
+      <c r="V45" t="s">
+        <v>168</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45"/>
+      <c r="Z45" t="n">
+        <v>0.0000045</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.00000035</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45"/>
+      <c r="AF45" t="n">
+        <v>-28.3</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AK45"/>
+      <c r="AL45"/>
+      <c r="AM45"/>
+      <c r="AN45" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AP45" t="s">
+        <v>169</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AS45" t="s">
+        <v>170</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="s">
+        <v>171</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="s">
+        <v>172</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BB45" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE45" t="s">
+        <v>170</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BH45" t="s">
+        <v>170</v>
+      </c>
+      <c r="BI45" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="46">
       <c r="H46" s="22"/>
